--- a/T41_V012_Files/T41_V012_BOMs/Source Files/T41_RF_Board_BOM_V012.8_09-12-26.xlsx
+++ b/T41_V012_Files/T41_V012_BOMs/Source Files/T41_RF_Board_BOM_V012.8_09-12-26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bill\Documents\GitHub\T41\T41_V012_Files\T41_V012_BOMs\Source Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A1DED7-F493-4F94-B6A0-B750B12C52CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC76E2EF-3B86-4C11-9FDF-6598C912A942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="743" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="As Second RX" sheetId="9" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Complete RF Board'!$A$1:$H$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Complete RF Board'!$A$1:$H$57</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -915,9 +915,6 @@
     <t>C33, C46</t>
   </si>
   <si>
-    <t>C33, C37</t>
-  </si>
-  <si>
     <t>10 nF 50V SMD 1206 Capacitor</t>
   </si>
   <si>
@@ -934,6 +931,9 @@
   </si>
   <si>
     <t>R7, R9, R12, R15, R19, R20, R21, R23</t>
+  </si>
+  <si>
+    <t>C37, C54</t>
   </si>
 </sst>
 </file>
@@ -1553,7 +1553,7 @@
         <v>286</v>
       </c>
       <c r="D5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G5" s="5">
         <v>0.13</v>
@@ -1568,13 +1568,13 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="D6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G6" s="5">
         <v>0.11</v>
@@ -2123,7 +2123,7 @@
         <v>110</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D24" t="s">
         <v>111</v>
@@ -2999,7 +2999,7 @@
         <v>54</v>
       </c>
       <c r="F52" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G52" s="5">
         <v>0.7</v>
@@ -3527,7 +3527,7 @@
         <v>110</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D21" t="s">
         <v>111</v>
@@ -3812,7 +3812,7 @@
         <v>54</v>
       </c>
       <c r="F34" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G34" s="5">
         <v>0.7</v>

--- a/T41_V012_Files/T41_V012_BOMs/Source Files/T41_RF_Board_BOM_V012.8_09-12-26.xlsx
+++ b/T41_V012_Files/T41_V012_BOMs/Source Files/T41_RF_Board_BOM_V012.8_09-12-26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bill\Documents\GitHub\T41\T41_V012_Files\T41_V012_BOMs\Source Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC76E2EF-3B86-4C11-9FDF-6598C912A942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6EBC54-A64D-4A8C-A9E8-31120366E9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="743" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -933,7 +933,7 @@
     <t>R7, R9, R12, R15, R19, R20, R21, R23</t>
   </si>
   <si>
-    <t>C37, C54</t>
+    <t>C4, C10, C17, C28, C37, C54</t>
   </si>
 </sst>
 </file>
@@ -1565,7 +1565,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>287</v>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="H6" s="5">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -3056,14 +3056,14 @@
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <f>SUM(A2:A54)</f>
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D55" t="s">
         <v>54</v>
       </c>
       <c r="H55" s="10">
         <f>SUM(H2:H54)</f>
-        <v>92.921000000000006</v>
+        <v>93.361000000000004</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">

--- a/T41_V012_Files/T41_V012_BOMs/Source Files/T41_RF_Board_BOM_V012.8_09-12-26.xlsx
+++ b/T41_V012_Files/T41_V012_BOMs/Source Files/T41_RF_Board_BOM_V012.8_09-12-26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bill\Documents\GitHub\T41\T41_V012_Files\T41_V012_BOMs\Source Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6EBC54-A64D-4A8C-A9E8-31120366E9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F33760-FB2A-43B4-AFE0-F943A339FA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="743" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="As Second RX" sheetId="9" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Complete RF Board'!$A$1:$H$57</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Complete RF Board'!$A$1:$H$58</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="297">
   <si>
     <t>Qty</t>
   </si>
@@ -418,9 +418,6 @@
   </si>
   <si>
     <t>2.2K Ohm SMD 1206 Resistor</t>
-  </si>
-  <si>
-    <t>R26, R34, R49, R50, R51, R52, R60, R61, R62, R63</t>
   </si>
   <si>
     <t>71-CRCW12062K20JNEAC</t>
@@ -934,6 +931,18 @@
   </si>
   <si>
     <t>C4, C10, C17, C28, C37, C54</t>
+  </si>
+  <si>
+    <t>R52</t>
+  </si>
+  <si>
+    <t>1.1k Ohm SMD 1206 Resistor</t>
+  </si>
+  <si>
+    <t>R26, R34, R49, R50, R51, R60, R61, R62, R63</t>
+  </si>
+  <si>
+    <t>71-CRCW1206J-1.1K-E3</t>
   </si>
 </sst>
 </file>
@@ -1401,7 +1410,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="1" customWidth="1"/>
@@ -1463,7 +1472,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -1472,7 +1481,7 @@
         <v>0.13900000000000001</v>
       </c>
       <c r="H2" s="5">
-        <f t="shared" ref="H2:H31" si="0">G2*A2</f>
+        <f t="shared" ref="H2:H32" si="0">G2*A2</f>
         <v>2.085</v>
       </c>
       <c r="I2" t="s">
@@ -1493,13 +1502,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>260</v>
-      </c>
       <c r="D3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G3" s="5">
         <v>0.1</v>
@@ -1547,13 +1556,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>286</v>
-      </c>
       <c r="D5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G5" s="5">
         <v>0.13</v>
@@ -1568,13 +1577,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G6" s="5">
         <v>0.11</v>
@@ -1589,13 +1598,13 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G7" s="5">
         <v>0.17</v>
@@ -1622,13 +1631,13 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D8" t="s">
         <v>253</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D8" t="s">
-        <v>254</v>
       </c>
       <c r="G8" s="5">
         <v>0.17</v>
@@ -1646,7 +1655,7 @@
         <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -1865,10 +1874,10 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F16" t="s">
         <v>70</v>
@@ -1889,7 +1898,7 @@
         <v>73</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D17" t="s">
         <v>74</v>
@@ -1952,16 +1961,16 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D19" t="s">
+        <v>256</v>
+      </c>
+      <c r="E19" t="s">
         <v>257</v>
-      </c>
-      <c r="E19" t="s">
-        <v>258</v>
       </c>
       <c r="G19" s="5">
         <v>0.47</v>
@@ -2123,7 +2132,7 @@
         <v>110</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D24" t="s">
         <v>111</v>
@@ -2216,200 +2225,188 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B27" t="s">
         <v>125</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D27" t="s">
         <v>126</v>
-      </c>
-      <c r="D27" t="s">
-        <v>127</v>
       </c>
       <c r="G27" s="5">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="H27" s="5">
         <f t="shared" si="0"/>
-        <v>0.36</v>
+        <v>0.32399999999999995</v>
       </c>
       <c r="I27" t="s">
+        <v>126</v>
+      </c>
+      <c r="J27" t="s">
         <v>127</v>
-      </c>
-      <c r="J27" t="s">
-        <v>128</v>
       </c>
       <c r="K27" t="s">
         <v>118</v>
       </c>
       <c r="L27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>130</v>
+        <v>294</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>132</v>
+        <v>293</v>
+      </c>
+      <c r="D28" t="s">
+        <v>296</v>
       </c>
       <c r="G28" s="5">
         <v>0.1</v>
       </c>
       <c r="H28" s="5">
         <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="I28" t="s">
-        <v>132</v>
-      </c>
-      <c r="J28" t="s">
-        <v>133</v>
-      </c>
-      <c r="K28" t="s">
-        <v>118</v>
-      </c>
-      <c r="L28" t="s">
-        <v>134</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D29" t="s">
-        <v>137</v>
+        <v>130</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="G29" s="5">
         <v>0.1</v>
       </c>
       <c r="H29" s="5">
         <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="I29" t="s">
+        <v>131</v>
+      </c>
+      <c r="J29" t="s">
+        <v>132</v>
+      </c>
+      <c r="K29" t="s">
+        <v>118</v>
+      </c>
+      <c r="L29" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D30" t="s">
+        <v>136</v>
+      </c>
+      <c r="G30" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="H30" s="5">
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I30" t="s">
+        <v>136</v>
+      </c>
+      <c r="J30" t="s">
         <v>137</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K30" t="s">
+        <v>103</v>
+      </c>
+      <c r="L30" t="s">
         <v>138</v>
       </c>
-      <c r="K29" t="s">
-        <v>103</v>
-      </c>
-      <c r="L29" t="s">
+    </row>
+    <row r="31" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>12</v>
+      </c>
+      <c r="B31" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
-        <v>12</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="C31" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D31" t="s">
+        <v>282</v>
+      </c>
+      <c r="G31" s="5">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="H31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.252</v>
+      </c>
+      <c r="I31" t="s">
         <v>140</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D30" t="s">
-        <v>283</v>
-      </c>
-      <c r="G30" s="5">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="H30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.252</v>
-      </c>
-      <c r="I30" t="s">
+      <c r="J31" t="s">
         <v>141</v>
-      </c>
-      <c r="J30" t="s">
-        <v>142</v>
-      </c>
-      <c r="K30" t="s">
-        <v>118</v>
-      </c>
-      <c r="L30" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
-        <v>2</v>
-      </c>
-      <c r="B31" t="s">
-        <v>144</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G31" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="H31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-      <c r="I31" t="s">
-        <v>145</v>
-      </c>
-      <c r="J31" t="s">
-        <v>146</v>
       </c>
       <c r="K31" t="s">
         <v>118</v>
       </c>
       <c r="L31" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>268</v>
+        <v>143</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>148</v>
+        <v>245</v>
       </c>
       <c r="D32" t="s">
-        <v>269</v>
+        <v>144</v>
       </c>
       <c r="G32" s="5">
         <v>0.1</v>
       </c>
       <c r="H32" s="5">
-        <f t="shared" ref="H32:H54" si="1">G32*A32</f>
-        <v>0.1</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="I32" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J32" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="K32" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="L32" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
@@ -2417,32 +2414,32 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>152</v>
+        <v>267</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D33" t="s">
-        <v>154</v>
+        <v>268</v>
       </c>
       <c r="G33" s="5">
         <v>0.1</v>
       </c>
       <c r="H33" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H33:H55" si="1">G33*A33</f>
         <v>0.1</v>
       </c>
       <c r="I33" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="J33" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="K33" t="s">
         <v>103</v>
       </c>
       <c r="L33" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
@@ -2450,13 +2447,13 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D34" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G34" s="5">
         <v>0.1</v>
@@ -2466,16 +2463,16 @@
         <v>0.1</v>
       </c>
       <c r="I34" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J34" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K34" t="s">
         <v>103</v>
       </c>
       <c r="L34" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -2483,13 +2480,13 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D35" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G35" s="5">
         <v>0.1</v>
@@ -2499,70 +2496,70 @@
         <v>0.1</v>
       </c>
       <c r="I35" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="J35" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="K35" t="s">
         <v>103</v>
       </c>
       <c r="L35" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="F36" t="s">
-        <v>168</v>
+        <v>162</v>
+      </c>
+      <c r="D36" t="s">
+        <v>163</v>
       </c>
       <c r="G36" s="5">
-        <v>2.8000000000000001E-2</v>
+        <v>0.1</v>
       </c>
       <c r="H36" s="5">
         <f t="shared" si="1"/>
-        <v>0.44800000000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+      <c r="I36" t="s">
+        <v>163</v>
+      </c>
+      <c r="J36" t="s">
+        <v>164</v>
+      </c>
+      <c r="K36" t="s">
+        <v>103</v>
+      </c>
+      <c r="L36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B37" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D37" t="s">
-        <v>171</v>
+        <v>269</v>
+      </c>
+      <c r="F37" t="s">
+        <v>167</v>
       </c>
       <c r="G37" s="5">
-        <v>4.0199999999999996</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="H37" s="5">
         <f t="shared" si="1"/>
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="I37" t="s">
-        <v>171</v>
-      </c>
-      <c r="J37" t="s">
-        <v>169</v>
-      </c>
-      <c r="K37" t="s">
-        <v>172</v>
-      </c>
-      <c r="L37" t="s">
-        <v>173</v>
+        <v>0.44800000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -2570,125 +2567,122 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D38" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G38" s="5">
-        <v>5.17</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="H38" s="5">
         <f t="shared" si="1"/>
-        <v>5.17</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="I38" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="J38" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="K38" t="s">
+        <v>171</v>
+      </c>
+      <c r="L38" t="s">
         <v>172</v>
-      </c>
-      <c r="L38" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D39" t="s">
-        <v>179</v>
-      </c>
-      <c r="E39" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G39" s="5">
-        <v>0.85</v>
+        <v>5.17</v>
       </c>
       <c r="H39" s="5">
         <f t="shared" si="1"/>
-        <v>1.7</v>
+        <v>5.17</v>
+      </c>
+      <c r="I39" t="s">
+        <v>175</v>
+      </c>
+      <c r="J39" t="s">
+        <v>173</v>
+      </c>
+      <c r="K39" t="s">
+        <v>171</v>
+      </c>
+      <c r="L39" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D40" t="s">
-        <v>183</v>
+        <v>178</v>
+      </c>
+      <c r="E40" t="s">
+        <v>179</v>
       </c>
       <c r="G40" s="5">
-        <v>3.6</v>
+        <v>0.85</v>
       </c>
       <c r="H40" s="5">
         <f t="shared" si="1"/>
-        <v>3.6</v>
-      </c>
-      <c r="I40" t="s">
-        <v>183</v>
-      </c>
-      <c r="J40" t="s">
-        <v>181</v>
-      </c>
-      <c r="K40" t="s">
-        <v>172</v>
-      </c>
-      <c r="L40" t="s">
-        <v>184</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="E41" t="s">
-        <v>54</v>
+        <v>181</v>
+      </c>
+      <c r="D41" t="s">
+        <v>182</v>
       </c>
       <c r="G41" s="5">
-        <v>0.33</v>
+        <v>3.6</v>
       </c>
       <c r="H41" s="5">
         <f t="shared" si="1"/>
-        <v>0.66</v>
+        <v>3.6</v>
       </c>
       <c r="I41" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="J41" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="K41" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="L41" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -2696,119 +2690,122 @@
         <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D42" t="s">
-        <v>192</v>
+        <v>230</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="E42" t="s">
+        <v>54</v>
       </c>
       <c r="G42" s="5">
-        <v>0.84</v>
+        <v>0.33</v>
       </c>
       <c r="H42" s="5">
         <f t="shared" si="1"/>
-        <v>1.68</v>
+        <v>0.66</v>
       </c>
       <c r="I42" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="J42" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="K42" t="s">
+        <v>188</v>
+      </c>
+      <c r="L42" t="s">
         <v>189</v>
-      </c>
-      <c r="L42" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
       <c r="D43" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G43" s="5">
-        <v>0.47</v>
+        <v>0.84</v>
       </c>
       <c r="H43" s="5">
         <f t="shared" si="1"/>
-        <v>0.47</v>
+        <v>1.68</v>
+      </c>
+      <c r="I43" t="s">
+        <v>192</v>
+      </c>
+      <c r="J43" t="s">
+        <v>193</v>
+      </c>
+      <c r="K43" t="s">
+        <v>188</v>
+      </c>
+      <c r="L43" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D44" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G44" s="5">
-        <v>1.03</v>
+        <v>0.47</v>
       </c>
       <c r="H44" s="5">
         <f t="shared" si="1"/>
-        <v>2.06</v>
-      </c>
-      <c r="I44" t="s">
-        <v>200</v>
-      </c>
-      <c r="J44" t="s">
-        <v>201</v>
-      </c>
-      <c r="K44" t="s">
-        <v>202</v>
-      </c>
-      <c r="L44" t="s">
-        <v>203</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="D45" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G45" s="5">
-        <v>1.87</v>
+        <v>1.03</v>
       </c>
       <c r="H45" s="5">
         <f t="shared" si="1"/>
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="I45" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J45" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K45" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="L45" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
@@ -2816,32 +2813,32 @@
         <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D46" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G46" s="5">
-        <v>2.46</v>
+        <v>1.87</v>
       </c>
       <c r="H46" s="5">
         <f t="shared" si="1"/>
-        <v>2.46</v>
+        <v>1.87</v>
       </c>
       <c r="I46" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="J46" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="K46" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="L46" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
@@ -2849,32 +2846,32 @@
         <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D47" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G47" s="5">
-        <v>1.69</v>
+        <v>2.46</v>
       </c>
       <c r="H47" s="5">
         <f t="shared" si="1"/>
-        <v>1.69</v>
+        <v>2.46</v>
       </c>
       <c r="I47" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="J47" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="K47" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L47" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
@@ -2882,32 +2879,32 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D48" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="G48" s="5">
-        <v>0.46</v>
+        <v>1.69</v>
       </c>
       <c r="H48" s="5">
         <f t="shared" si="1"/>
-        <v>0.46</v>
+        <v>1.69</v>
       </c>
       <c r="I48" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="J48" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K48" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="L48" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
@@ -2915,32 +2912,32 @@
         <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="D49" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="G49" s="5">
-        <v>1.42</v>
+        <v>0.46</v>
       </c>
       <c r="H49" s="5">
         <f t="shared" si="1"/>
-        <v>1.42</v>
+        <v>0.46</v>
       </c>
       <c r="I49" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="J49" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="K49" t="s">
-        <v>228</v>
+        <v>92</v>
       </c>
       <c r="L49" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
@@ -2948,20 +2945,32 @@
         <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>264</v>
+        <v>223</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>261</v>
+        <v>224</v>
       </c>
       <c r="D50" t="s">
-        <v>267</v>
+        <v>225</v>
       </c>
       <c r="G50" s="5">
-        <v>9.9600000000000009</v>
+        <v>1.42</v>
       </c>
       <c r="H50" s="5">
         <f t="shared" si="1"/>
-        <v>9.9600000000000009</v>
+        <v>1.42</v>
+      </c>
+      <c r="I50" t="s">
+        <v>225</v>
+      </c>
+      <c r="J50" t="s">
+        <v>226</v>
+      </c>
+      <c r="K50" t="s">
+        <v>227</v>
+      </c>
+      <c r="L50" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
@@ -2969,106 +2978,127 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D51" t="s">
         <v>266</v>
       </c>
       <c r="G51" s="5">
-        <v>4</v>
+        <v>9.9600000000000009</v>
       </c>
       <c r="H51" s="5">
         <f t="shared" si="1"/>
+        <v>9.9600000000000009</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>1</v>
+      </c>
+      <c r="B52" t="s">
+        <v>264</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D52" t="s">
+        <v>265</v>
+      </c>
+      <c r="G52" s="5">
         <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
-        <v>1</v>
-      </c>
-      <c r="B52" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F52" t="s">
-        <v>291</v>
-      </c>
-      <c r="G52" s="5">
-        <v>0.7</v>
       </c>
       <c r="H52" s="5">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>272</v>
+        <v>247</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D53" s="12"/>
+        <v>248</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="F53" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="G53" s="5">
-        <v>5.84</v>
+        <v>0.7</v>
       </c>
       <c r="H53" s="5">
         <f t="shared" si="1"/>
-        <v>11.68</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="8">
-        <v>1</v>
+      <c r="A54" s="1">
+        <v>2</v>
       </c>
       <c r="B54" s="13" t="s">
         <v>271</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>233</v>
+        <v>272</v>
       </c>
       <c r="D54" s="12"/>
       <c r="F54" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G54" s="5">
+        <v>5.84</v>
+      </c>
+      <c r="H54" s="5">
+        <f t="shared" si="1"/>
+        <v>11.68</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="8">
+        <v>1</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D55" s="12"/>
+      <c r="F55" t="s">
+        <v>273</v>
+      </c>
+      <c r="G55" s="5">
         <v>11.74</v>
       </c>
-      <c r="H54" s="9">
+      <c r="H55" s="9">
         <f t="shared" si="1"/>
         <v>11.74</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="1">
-        <f>SUM(A2:A54)</f>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <f>SUM(A2:A55)</f>
         <v>197</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D56" t="s">
         <v>54</v>
       </c>
-      <c r="H55" s="10">
-        <f>SUM(H2:H54)</f>
-        <v>93.361000000000004</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B57" s="11" t="s">
-        <v>247</v>
+      <c r="H56" s="10">
+        <f>SUM(H2:H55)</f>
+        <v>93.424999999999997</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B58" s="11" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -3128,7 +3158,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -3170,7 +3200,7 @@
         <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D4" t="s">
         <v>23</v>
@@ -3188,13 +3218,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G5" s="5">
         <v>0.17</v>
@@ -3209,13 +3239,13 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D6" t="s">
         <v>253</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D6" t="s">
-        <v>254</v>
       </c>
       <c r="G6" s="5">
         <v>0.17</v>
@@ -3233,7 +3263,7 @@
         <v>27</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -3272,10 +3302,10 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D9" t="s">
         <v>47</v>
@@ -3293,10 +3323,10 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D10" t="s">
         <v>53</v>
@@ -3401,7 +3431,7 @@
         <v>73</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D15" t="s">
         <v>74</v>
@@ -3422,7 +3452,7 @@
         <v>78</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D16" t="s">
         <v>80</v>
@@ -3440,13 +3470,13 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G17" s="5">
         <v>0.47</v>
@@ -3506,7 +3536,7 @@
         <v>105</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D20" t="s">
         <v>107</v>
@@ -3527,7 +3557,7 @@
         <v>110</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D21" t="s">
         <v>111</v>
@@ -3566,13 +3596,13 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G23" s="5">
         <v>2.1000000000000001E-2</v>
@@ -3587,13 +3617,13 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
+        <v>166</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F24" t="s">
         <v>167</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F24" t="s">
-        <v>168</v>
       </c>
       <c r="G24" s="5">
         <v>2.8000000000000001E-2</v>
@@ -3608,13 +3638,13 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
+        <v>168</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" t="s">
         <v>170</v>
-      </c>
-      <c r="D25" t="s">
-        <v>171</v>
       </c>
       <c r="G25" s="5">
         <v>4.0199999999999996</v>
@@ -3629,16 +3659,16 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D26" t="s">
+        <v>178</v>
+      </c>
+      <c r="E26" t="s">
         <v>179</v>
-      </c>
-      <c r="E26" t="s">
-        <v>180</v>
       </c>
       <c r="G26" s="5">
         <v>0.85</v>
@@ -3653,13 +3683,13 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
+        <v>180</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" t="s">
         <v>182</v>
-      </c>
-      <c r="D27" t="s">
-        <v>183</v>
       </c>
       <c r="G27" s="5">
         <v>3.6</v>
@@ -3674,13 +3704,13 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E28" t="s">
         <v>54</v>
@@ -3698,13 +3728,13 @@
         <v>2</v>
       </c>
       <c r="B29" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D29" t="s">
         <v>191</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D29" t="s">
-        <v>192</v>
       </c>
       <c r="G29" s="5">
         <v>0.84</v>
@@ -3719,13 +3749,13 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
+        <v>208</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" t="s">
         <v>210</v>
-      </c>
-      <c r="D30" t="s">
-        <v>211</v>
       </c>
       <c r="G30" s="5">
         <v>2.46</v>
@@ -3740,13 +3770,13 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
+        <v>212</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" t="s">
         <v>214</v>
-      </c>
-      <c r="D31" t="s">
-        <v>215</v>
       </c>
       <c r="G31" s="5">
         <v>1.69</v>
@@ -3761,13 +3791,13 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G32" s="5">
         <v>9.9600000000000009</v>
@@ -3782,13 +3812,13 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
+        <v>264</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D33" t="s">
         <v>265</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D33" t="s">
-        <v>266</v>
       </c>
       <c r="G33" s="5">
         <v>4</v>
@@ -3803,16 +3833,16 @@
         <v>1</v>
       </c>
       <c r="B34" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>54</v>
       </c>
       <c r="F34" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G34" s="5">
         <v>0.7</v>
@@ -3827,14 +3857,14 @@
         <v>1</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D35" s="12"/>
       <c r="F35" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G35" s="5">
         <v>5.84</v>
@@ -3849,14 +3879,14 @@
         <v>1</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D36" s="12"/>
       <c r="F36" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G36" s="5">
         <v>11.74</v>
